--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_23_6.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_23_6.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_4</t>
+          <t>model_23_6_1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9824950532297048</v>
+        <v>0.9998812132072559</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8377418809667536</v>
+        <v>0.6475108694845076</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9302093413852592</v>
+        <v>0.9988770600880047</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9459413092727226</v>
+        <v>0.9999973317574914</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9638466630421146</v>
+        <v>0.9998573853036785</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1170556596558323</v>
+        <v>7.051697149515868e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.085020789105258</v>
+        <v>0.2092527746115909</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005722332519569933</v>
+        <v>0.0001831963358876928</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4027492787763245</v>
+        <v>2.102790756724864e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2042357998894299</v>
+        <v>9.264955658152696e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3327196531754841</v>
+        <v>0.002487615848120643</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3421339791015098</v>
+        <v>0.008397438388887332</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003653206282496</v>
+        <v>1.000050015491682</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3566993309068339</v>
+        <v>0.00875493472619614</v>
       </c>
       <c r="P2" t="n">
-        <v>282.2902114675016</v>
+        <v>181.1193142933784</v>
       </c>
       <c r="Q2" t="n">
-        <v>451.7139511241815</v>
+        <v>279.8482561077026</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_5</t>
+          <t>model_23_6_0</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9847658567060861</v>
+        <v>0.9998776684844908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8375852863180214</v>
+        <v>0.6473845064106581</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9163915139006688</v>
+        <v>0.9988668563554814</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9505905964728609</v>
+        <v>0.9999969830630179</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9668121763442784</v>
+        <v>0.9998558926147018</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1018707863531823</v>
+        <v>7.262127205261973e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.086067938242382</v>
+        <v>0.2093277891908285</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00685529508410688</v>
+        <v>0.0001848609720722905</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3681110542561204</v>
+        <v>2.377590185034887e-06</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1874831559479953</v>
+        <v>9.361928112866269e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3200347006393538</v>
+        <v>0.002460977688146827</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3191720325360326</v>
+        <v>0.008521811547588912</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003179299470034</v>
+        <v>1.00005150800653</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3327598467382822</v>
+        <v>0.008884602707751578</v>
       </c>
       <c r="P3" t="n">
-        <v>282.5681001384537</v>
+        <v>181.0605053511421</v>
       </c>
       <c r="Q3" t="n">
-        <v>451.9918397951336</v>
+        <v>279.7894471654663</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_3</t>
+          <t>model_23_6_2</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9795496273588239</v>
+        <v>0.9999064811082717</v>
       </c>
       <c r="C4" t="n">
-        <v>0.837483594258521</v>
+        <v>0.6472832838220761</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9439878795749392</v>
+        <v>0.9991627204368877</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9394434996510725</v>
+        <v>0.9999961908045194</v>
       </c>
       <c r="F4" t="n">
-        <v>0.959661934251085</v>
+        <v>0.9998925607611403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1367517360168524</v>
+        <v>5.551685393569982e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.086747953512511</v>
+        <v>0.2093878792919989</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004592591394899003</v>
+        <v>0.0001365937272665559</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4511594067971448</v>
+        <v>3.001953915871544e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2278759809590742</v>
+        <v>6.97978405912137e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3466733376728653</v>
+        <v>0.002288728668553371</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3697995889895666</v>
+        <v>0.007450963289112343</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00426790385555</v>
+        <v>1.000039376375464</v>
       </c>
       <c r="O4" t="n">
-        <v>0.3855427230835328</v>
+        <v>0.007768166221950173</v>
       </c>
       <c r="P4" t="n">
-        <v>281.9791762858781</v>
+        <v>181.5976478175891</v>
       </c>
       <c r="Q4" t="n">
-        <v>451.4029159425579</v>
+        <v>280.3265896319133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_6</t>
+          <t>model_23_6_3</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9865028494395455</v>
+        <v>0.9999263559885135</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8371288718753085</v>
+        <v>0.6470585263492082</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9027745837030787</v>
+        <v>0.9993814979600671</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9538099723866836</v>
+        <v>0.9999949717656719</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9688362476833401</v>
+        <v>0.9999192910608872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09025550794642355</v>
+        <v>4.371826647404757e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.089119983722399</v>
+        <v>0.2095213050369106</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007971785514674701</v>
+        <v>0.0001009023779851504</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3441259871011785</v>
+        <v>3.962655056196943e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1760488634662784</v>
+        <v>5.243251652067369e-05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3085138369502005</v>
+        <v>0.002127289232807781</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3004255447634631</v>
+        <v>0.006611979013430667</v>
       </c>
       <c r="N5" t="n">
-        <v>1.002816796638704</v>
+        <v>1.000031008004836</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3132152821706549</v>
+        <v>0.006893464648715854</v>
       </c>
       <c r="P5" t="n">
-        <v>282.8102213075082</v>
+        <v>182.0754890921628</v>
       </c>
       <c r="Q5" t="n">
-        <v>452.2339609641881</v>
+        <v>280.804430906487</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_2</t>
+          <t>model_23_6_4</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9757528802680832</v>
+        <v>0.9999419641510101</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8366633598900329</v>
+        <v>0.6468411523629142</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9574180614516978</v>
+        <v>0.9995482354587777</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9305652957136286</v>
+        <v>0.9999937478079156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9539050225967617</v>
+        <v>0.9999394842331545</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1621406012950486</v>
+        <v>3.445258697856244e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.092232864511422</v>
+        <v>0.2096503476252421</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003491412984743094</v>
+        <v>7.370083452538615e-05</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5173040023196999</v>
+        <v>4.927232694172701e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2603976665225159</v>
+        <v>3.931403360977942e-05</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3620136847121825</v>
+        <v>0.001997077514197683</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4026668614314426</v>
+        <v>0.0058696326101863</v>
       </c>
       <c r="N6" t="n">
-        <v>1.005060268465791</v>
+        <v>1.000024436146943</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4198092233578929</v>
+        <v>0.006119515022216474</v>
       </c>
       <c r="P6" t="n">
-        <v>281.638582821873</v>
+        <v>182.5518529392133</v>
       </c>
       <c r="Q6" t="n">
-        <v>451.0623224785529</v>
+        <v>281.2807947535375</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_7</t>
+          <t>model_23_6_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9878183301676217</v>
+        <v>0.9999542045541128</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8364621750204159</v>
+        <v>0.6466318358969907</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8895343751901628</v>
+        <v>0.9996746291462349</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9559291433499221</v>
+        <v>0.9999925799826332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9701375526084094</v>
+        <v>0.9999546458016187</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08145888226054575</v>
+        <v>2.71861549389299e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.093578188660923</v>
+        <v>0.2097746069214148</v>
       </c>
       <c r="I7" t="n">
-        <v>0.00905738747406562</v>
+        <v>5.308097751063272e-05</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3283376917213698</v>
+        <v>5.84757340585149e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1686975903989766</v>
+        <v>2.946432925580132e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2980625339720844</v>
+        <v>0.001876882620117835</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2854100248073738</v>
+        <v>0.005214034420573948</v>
       </c>
       <c r="N7" t="n">
-        <v>1.002542261530236</v>
+        <v>1.000019282293005</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2975605204436236</v>
+        <v>0.00543600666039698</v>
       </c>
       <c r="P7" t="n">
-        <v>283.0153137963699</v>
+        <v>183.0256054476997</v>
       </c>
       <c r="Q7" t="n">
-        <v>452.4390534530497</v>
+        <v>281.7545472620239</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_8</t>
+          <t>model_23_6_6</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9888019040140802</v>
+        <v>0.9999637886036277</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8356544947203953</v>
+        <v>0.6464313464977447</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8768007576983603</v>
+        <v>0.9997698201096081</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9572081864695807</v>
+        <v>0.9999914962485532</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9708885699394924</v>
+        <v>0.9999659407275231</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07488171942033629</v>
+        <v>2.149664913748103e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.098979150546186</v>
+        <v>0.2098936260894983</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01010145260987902</v>
+        <v>3.755153064235727e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3188085357792629</v>
+        <v>6.701643453477124e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1644549771784259</v>
+        <v>2.212658704791719e-05</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2885882378052124</v>
+        <v>0.001765724576873738</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2736452437378298</v>
+        <v>0.004636447900869914</v>
       </c>
       <c r="N8" t="n">
-        <v>1.002336993944888</v>
+        <v>1.000015246903736</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2852948882874949</v>
+        <v>0.004833831086780221</v>
       </c>
       <c r="P8" t="n">
-        <v>283.1836909694644</v>
+        <v>183.4952269780956</v>
       </c>
       <c r="Q8" t="n">
-        <v>452.6074306261443</v>
+        <v>282.2241687924198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_1</t>
+          <t>model_23_6_7</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9708828967163698</v>
+        <v>0.999971268448158</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8350934798477504</v>
+        <v>0.6462408545484526</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9700937115706537</v>
+        <v>0.9998407882533926</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9186305766983025</v>
+        <v>0.9999904999162434</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9461271270412591</v>
+        <v>0.9999742471670438</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1947062037295677</v>
+        <v>1.705629031186732e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.102730659582799</v>
+        <v>0.2100067103394218</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00245210075697352</v>
+        <v>2.597379280688997e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6062203155184441</v>
+        <v>7.486833841854106e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3043362031528956</v>
+        <v>1.673031332437204e-05</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3788500241256489</v>
+        <v>0.001663533832735033</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4412552591523048</v>
+        <v>0.004129926187217795</v>
       </c>
       <c r="N9" t="n">
-        <v>1.006076612859192</v>
+        <v>1.000012097495512</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4600404090587275</v>
+        <v>0.004305745695133438</v>
       </c>
       <c r="P9" t="n">
-        <v>281.2725270081876</v>
+        <v>183.9579829780531</v>
       </c>
       <c r="Q9" t="n">
-        <v>450.6962666648674</v>
+        <v>282.6869247923773</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_9</t>
+          <t>model_23_6_8</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9895250202052311</v>
+        <v>0.9999770740269831</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8347590810672022</v>
+        <v>0.6460606930370665</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8646585102548159</v>
+        <v>0.9998927552447182</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9578515064462673</v>
+        <v>0.9999895977291026</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9712246586201814</v>
+        <v>0.9999802249255247</v>
       </c>
       <c r="G10" t="n">
-        <v>0.07004623812046647</v>
+        <v>1.360984793329745e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.104966785768089</v>
+        <v>0.2101136619951526</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0110970296510761</v>
+        <v>1.749590160696175e-05</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3140156587571385</v>
+        <v>8.197830227912627e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1625563601679333</v>
+        <v>1.284686591743719e-05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2800090814366663</v>
+        <v>0.001569143918558831</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2646624985154989</v>
+        <v>0.00368915273922041</v>
       </c>
       <c r="N10" t="n">
-        <v>1.002186082739778</v>
+        <v>1.00000965304127</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2759297290042034</v>
+        <v>0.00384620760892798</v>
       </c>
       <c r="P10" t="n">
-        <v>283.3171994208365</v>
+        <v>184.4094338290459</v>
       </c>
       <c r="Q10" t="n">
-        <v>452.7409390775163</v>
+        <v>283.1383756433701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_10</t>
+          <t>model_23_6_9</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9900445796073476</v>
+        <v>0.9999815550439898</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8338165292030866</v>
+        <v>0.6458916848649704</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8531711290644483</v>
+        <v>0.9999300887435658</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9580196120792563</v>
+        <v>0.9999887766872292</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9712521497390264</v>
+        <v>0.9999844153140115</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06657194200616229</v>
+        <v>1.094972266825043e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.111269634423482</v>
+        <v>0.2102139925468818</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01203891236511102</v>
+        <v>1.14053173097215e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3127632343729418</v>
+        <v>8.844877584579471e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1624010585797646</v>
+        <v>1.01245824135779e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2722453621654565</v>
+        <v>0.001482239373952582</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2580153910257337</v>
+        <v>0.00330903651660879</v>
       </c>
       <c r="N11" t="n">
-        <v>1.00207765295151</v>
+        <v>1.000007766297268</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2689996403871895</v>
+        <v>0.003449909051770728</v>
       </c>
       <c r="P11" t="n">
-        <v>283.4189441628052</v>
+        <v>184.8443928582458</v>
       </c>
       <c r="Q11" t="n">
-        <v>452.8426838194851</v>
+        <v>283.5733346725701</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_11</t>
+          <t>model_23_6_10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9904059035502013</v>
+        <v>0.9999849884318237</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8328572986393445</v>
+        <v>0.6457331030752349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8423666680129425</v>
+        <v>0.9999560795881691</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9578382540233161</v>
+        <v>0.9999880394474689</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9710541642244038</v>
+        <v>0.999987230763187</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06415576713655576</v>
+        <v>8.91151533543097e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>1.117684013620076</v>
+        <v>0.2103081335476454</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01292480053494124</v>
+        <v>7.165172804128816e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3141143922579652</v>
+        <v>9.425882102886893e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1635195094157843</v>
+        <v>8.295527453507853e-06</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2652131062300266</v>
+        <v>0.001402248418126149</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2532898875528902</v>
+        <v>0.002985216128763706</v>
       </c>
       <c r="N12" t="n">
-        <v>1.00200224621561</v>
+        <v>1.000006320660285</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2640729624483663</v>
+        <v>0.003112302959614467</v>
       </c>
       <c r="P12" t="n">
-        <v>283.4928825823153</v>
+        <v>185.2563325192509</v>
       </c>
       <c r="Q12" t="n">
-        <v>452.9166222389952</v>
+        <v>283.9852743335751</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_6_0</t>
+          <t>model_23_6_11</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.964660437771946</v>
+        <v>0.9999875881621906</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8325349746491132</v>
+        <v>0.6455856987939388</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9814871688083947</v>
+        <v>0.9999732646042265</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9027778616997039</v>
+        <v>0.9999873721762655</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9357563665756787</v>
+        <v>0.9999889837845237</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2363158153427185</v>
+        <v>7.368203087157494e-06</v>
       </c>
       <c r="H13" t="n">
-        <v>1.119839395626919</v>
+        <v>0.2103956390965562</v>
       </c>
       <c r="I13" t="n">
-        <v>0.001517919132155265</v>
+        <v>4.361610529548289e-06</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7243265708945221</v>
+        <v>9.951745743185234e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3629222352421833</v>
+        <v>7.156678136366761e-06</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3973205550693175</v>
+        <v>0.001328898996525331</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4861232511850452</v>
+        <v>0.002714443421248174</v>
       </c>
       <c r="N13" t="n">
-        <v>1.007375212986724</v>
+        <v>1.000005226036972</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5068185244018494</v>
+        <v>0.002830002897363222</v>
       </c>
       <c r="P13" t="n">
-        <v>280.8851723358884</v>
+        <v>185.6366733919751</v>
       </c>
       <c r="Q13" t="n">
-        <v>450.3089119925683</v>
+        <v>284.3656152062994</v>
       </c>
     </row>
     <row r="14">
@@ -1177,52 +1177,52 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.990645061844331</v>
+        <v>0.9999895367454609</v>
       </c>
       <c r="C14" t="n">
-        <v>0.831904053494702</v>
+        <v>0.6454482418308973</v>
       </c>
       <c r="D14" t="n">
-        <v>0.832267717563631</v>
+        <v>0.9999837789843511</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9574059735873449</v>
+        <v>0.9999867768821447</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9706958091823272</v>
+        <v>0.9999899428982141</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06255651452248805</v>
+        <v>6.211439883459401e-06</v>
       </c>
       <c r="H14" t="n">
-        <v>1.124058368291591</v>
+        <v>0.2104772394876492</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01375284190489923</v>
+        <v>2.646295317771234e-06</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3173349777267264</v>
+        <v>1.042088562491924e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1655439125503607</v>
+        <v>6.533590471345237e-06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2588617516623335</v>
+        <v>0.00126132487911879</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2501130035053916</v>
+        <v>0.002492276044795079</v>
       </c>
       <c r="N14" t="n">
-        <v>1.001952334919444</v>
+        <v>1.000004405580859</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2607608318699091</v>
+        <v>0.002598377395744648</v>
       </c>
       <c r="P14" t="n">
-        <v>283.5433697969036</v>
+        <v>185.9782356472082</v>
       </c>
       <c r="Q14" t="n">
-        <v>452.9671094535834</v>
+        <v>284.7071774615325</v>
       </c>
     </row>
     <row r="15">
@@ -1232,52 +1232,52 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9907905755582193</v>
+        <v>0.9999909698731527</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8309731231875261</v>
+        <v>0.6453213163967496</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8228621112120271</v>
+        <v>0.9999892035141271</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9567986981152776</v>
+        <v>0.9999862348872741</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9702271111194246</v>
+        <v>0.9999902943942741</v>
       </c>
       <c r="G15" t="n">
-        <v>0.06158346364768828</v>
+        <v>5.360673377692207e-06</v>
       </c>
       <c r="H15" t="n">
-        <v>1.130283503542216</v>
+        <v>0.2105525879082525</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01452403404092943</v>
+        <v>1.761337923114008e-06</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3218593151663349</v>
+        <v>1.084802138950105e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1681916604994654</v>
+        <v>6.305241255298309e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2531171182778306</v>
+        <v>0.0011994917061997</v>
       </c>
       <c r="M15" t="n">
-        <v>0.248160157252707</v>
+        <v>0.002315312803422511</v>
       </c>
       <c r="N15" t="n">
-        <v>1.001921966840024</v>
+        <v>1.000003802158673</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2587248489092987</v>
+        <v>0.00241388046282244</v>
       </c>
       <c r="P15" t="n">
-        <v>283.5747237835178</v>
+        <v>186.2728419212118</v>
       </c>
       <c r="Q15" t="n">
-        <v>452.9984634401976</v>
+        <v>285.001783735536</v>
       </c>
     </row>
     <row r="16">
@@ -1287,52 +1287,52 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9908650612149376</v>
+        <v>0.9999919995013853</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8300760720699881</v>
+        <v>0.6452037589497147</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8141407942890168</v>
+        <v>0.9999908182308629</v>
       </c>
       <c r="E16" t="n">
-        <v>0.956075577195491</v>
+        <v>0.9999857467356014</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9696869736823914</v>
+        <v>0.9999902019174725</v>
       </c>
       <c r="G16" t="n">
-        <v>0.06108537771823765</v>
+        <v>4.749441581210439e-06</v>
       </c>
       <c r="H16" t="n">
-        <v>1.136282088495733</v>
+        <v>0.2106223750870297</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01523911936083609</v>
+        <v>1.497913151818327e-06</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3272467269773502</v>
+        <v>1.123272436230626e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1712429805375359</v>
+        <v>6.365318757062295e-06</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2479338265346269</v>
+        <v>0.00114650867557434</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2471545624062758</v>
+        <v>0.002179321357948487</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001906422007317</v>
+        <v>1.000003368630996</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2576764438083865</v>
+        <v>0.002272099579973486</v>
       </c>
       <c r="P16" t="n">
-        <v>283.5909655173186</v>
+        <v>186.5149670173582</v>
       </c>
       <c r="Q16" t="n">
-        <v>453.0147051739985</v>
+        <v>285.2439088316824</v>
       </c>
     </row>
     <row r="17">
@@ -1342,52 +1342,52 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9908863031341006</v>
+        <v>0.9999927156816755</v>
       </c>
       <c r="C17" t="n">
-        <v>0.829220758012412</v>
+        <v>0.6450955949709476</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8060789583343539</v>
+        <v>0.9999896126609314</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9552814662211591</v>
+        <v>0.9999853076938928</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9691048455539547</v>
+        <v>0.9999897851354135</v>
       </c>
       <c r="G17" t="n">
-        <v>0.06094333290698425</v>
+        <v>4.324286023625556e-06</v>
       </c>
       <c r="H17" t="n">
-        <v>1.142001577537104</v>
+        <v>0.2106865858972665</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01590013198009601</v>
+        <v>1.694589743100332e-06</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3331630304963171</v>
+        <v>1.157872471406408e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1745315124948456</v>
+        <v>6.63608098530564e-06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2432527835770661</v>
+        <v>0.001125018545884544</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2468670348729944</v>
+        <v>0.002079491770511621</v>
       </c>
       <c r="N17" t="n">
-        <v>1.001901988911144</v>
+        <v>1.0000030670814</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2573766756327494</v>
+        <v>0.002168020040323698</v>
       </c>
       <c r="P17" t="n">
-        <v>283.5956216306113</v>
+        <v>186.702527024901</v>
       </c>
       <c r="Q17" t="n">
-        <v>453.0193612872912</v>
+        <v>285.4314688392252</v>
       </c>
     </row>
     <row r="18">
@@ -1397,52 +1397,52 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9908683617065445</v>
+        <v>0.9999931885962514</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8284120314141983</v>
+        <v>0.6449962983932203</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7986520133671362</v>
+        <v>0.9999863618933252</v>
       </c>
       <c r="E18" t="n">
-        <v>0.954450902986677</v>
+        <v>0.9999849111887168</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9685032651890377</v>
+        <v>0.9999891355846237</v>
       </c>
       <c r="G18" t="n">
-        <v>0.06106330731566507</v>
+        <v>4.043543502464357e-06</v>
       </c>
       <c r="H18" t="n">
-        <v>1.147409536023202</v>
+        <v>0.2107455326351942</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01650908810044978</v>
+        <v>2.224919734856213e-06</v>
       </c>
       <c r="J18" t="n">
-        <v>0.339350911467267</v>
+        <v>1.189120284018005e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1779299331487876</v>
+        <v>7.058061287518134e-06</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2390231575525464</v>
+        <v>0.001105034176112116</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2471099093837903</v>
+        <v>0.002010856410205452</v>
       </c>
       <c r="N18" t="n">
-        <v>1.001905733209069</v>
+        <v>1.000002867959473</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2576298898142894</v>
+        <v>0.002096462730634513</v>
       </c>
       <c r="P18" t="n">
-        <v>283.5916882562595</v>
+        <v>186.8367782917045</v>
       </c>
       <c r="Q18" t="n">
-        <v>453.0154279129393</v>
+        <v>285.5657201060288</v>
       </c>
     </row>
     <row r="19">
@@ -1452,52 +1452,52 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9908221424477651</v>
+        <v>0.999993474989032</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8276526334278443</v>
+        <v>0.6449051925347959</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7918275723949499</v>
+        <v>0.9999816883527843</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9536092965713527</v>
+        <v>0.9999845503974211</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9678987655789192</v>
+        <v>0.9999883301222333</v>
       </c>
       <c r="G19" t="n">
-        <v>0.06137237571194313</v>
+        <v>3.873528376416488e-06</v>
       </c>
       <c r="H19" t="n">
-        <v>1.152487633854657</v>
+        <v>0.2107996170083231</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01706864322255573</v>
+        <v>2.987360800107467e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3456210665935789</v>
+        <v>1.217553554205747e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1813448450710046</v>
+        <v>7.581329472549772e-06</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2352096420782862</v>
+        <v>0.001086490082311453</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2477344863194124</v>
+        <v>0.00196812814024303</v>
       </c>
       <c r="N19" t="n">
-        <v>1.001915378967423</v>
+        <v>1.000002747373039</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2582810562831134</v>
+        <v>0.002051915429760078</v>
       </c>
       <c r="P19" t="n">
-        <v>283.5815909040783</v>
+        <v>186.9226894822386</v>
       </c>
       <c r="Q19" t="n">
-        <v>453.0053305607582</v>
+        <v>285.6516312965629</v>
       </c>
     </row>
     <row r="20">
@@ -1507,52 +1507,52 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9907561979872668</v>
+        <v>0.9999936199025038</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8269435776840933</v>
+        <v>0.6448217875621434</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7855737040413524</v>
+        <v>0.9999760618430097</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9527755312213543</v>
+        <v>0.9999842270965239</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9673035825319485</v>
+        <v>0.999987427379175</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06181334662294176</v>
+        <v>3.787501479623094e-06</v>
       </c>
       <c r="H20" t="n">
-        <v>1.157229092878022</v>
+        <v>0.2108491298029969</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01758141548983653</v>
+        <v>3.905269197119026e-06</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3518328040378809</v>
+        <v>1.243032277975768e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.184707126285054</v>
+        <v>8.167795988438352e-06</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2317687448476661</v>
+        <v>0.001069268695286366</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2486229004394844</v>
+        <v>0.001946150425743882</v>
       </c>
       <c r="N20" t="n">
-        <v>1.001929141289614</v>
+        <v>1.000002686356841</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2592072920315476</v>
+        <v>0.002029002078454561</v>
       </c>
       <c r="P20" t="n">
-        <v>283.567271946126</v>
+        <v>186.9676079929386</v>
       </c>
       <c r="Q20" t="n">
-        <v>452.9910116028059</v>
+        <v>285.6965498072628</v>
       </c>
     </row>
     <row r="21">
@@ -1562,52 +1562,52 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9906771707907059</v>
+        <v>0.9999936555939314</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8262847034905958</v>
+        <v>0.6447459340811293</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7798532235997438</v>
+        <v>0.999969830007915</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9519637876044424</v>
+        <v>0.9999839249780335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9667267869832068</v>
+        <v>0.9999864616622425</v>
       </c>
       <c r="G21" t="n">
-        <v>0.06234180185023055</v>
+        <v>3.766313506429326e-06</v>
       </c>
       <c r="H21" t="n">
-        <v>1.161634987643777</v>
+        <v>0.2108941597060266</v>
       </c>
       <c r="I21" t="n">
-        <v>0.01805045378103939</v>
+        <v>4.92193032298706e-06</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3578804746688971</v>
+        <v>1.26684165688931e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1879655336737589</v>
+        <v>8.795173445940081e-06</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2286639448471617</v>
+        <v>0.001053761658525303</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2496834032334359</v>
+        <v>0.001940699231315694</v>
       </c>
       <c r="N21" t="n">
-        <v>1.00194563392194</v>
+        <v>1.000002671328871</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2603129426249811</v>
+        <v>0.002023318815394037</v>
       </c>
       <c r="P21" t="n">
-        <v>283.5502462029275</v>
+        <v>186.9788277693296</v>
       </c>
       <c r="Q21" t="n">
-        <v>452.9739858596074</v>
+        <v>285.7077695836539</v>
       </c>
     </row>
     <row r="22">
@@ -1617,52 +1617,52 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9905900316165656</v>
+        <v>0.9999936127000201</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8256748957537052</v>
+        <v>0.6446769133567363</v>
       </c>
       <c r="D22" t="n">
-        <v>0.7746246518961406</v>
+        <v>0.999963277086747</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9511830216213876</v>
+        <v>0.9999836521052042</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9661739937160162</v>
+        <v>0.9999854733685074</v>
       </c>
       <c r="G22" t="n">
-        <v>0.06292450190894629</v>
+        <v>3.791777185092656e-06</v>
       </c>
       <c r="H22" t="n">
-        <v>1.16571277478827</v>
+        <v>0.2109351333895663</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01847915909037878</v>
+        <v>5.990973407575052e-06</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3636973550324049</v>
+        <v>1.288346241316967e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1910883484565182</v>
+        <v>9.437217910372358e-06</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2258681300349687</v>
+        <v>0.001039558177534973</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2508475670779892</v>
+        <v>0.001947248619229875</v>
       </c>
       <c r="N22" t="n">
-        <v>1.001963819488717</v>
+        <v>1.000002689389465</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2615266673345484</v>
+        <v>0.002030147024310827</v>
       </c>
       <c r="P22" t="n">
-        <v>283.5316393072453</v>
+        <v>186.9653514690068</v>
       </c>
       <c r="Q22" t="n">
-        <v>452.9553789639252</v>
+        <v>285.694293283331</v>
       </c>
     </row>
     <row r="23">
@@ -1672,52 +1672,52 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9904986372422037</v>
+        <v>0.9999935122551254</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8251124315279469</v>
+        <v>0.6446143456494773</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7698580684336266</v>
+        <v>0.9999566167280074</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9504396840838886</v>
+        <v>0.9999833996447635</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9656492625860247</v>
+        <v>0.9999844839659084</v>
       </c>
       <c r="G23" t="n">
-        <v>0.06353565651113686</v>
+        <v>3.851405613502503e-06</v>
       </c>
       <c r="H23" t="n">
-        <v>1.169473975655826</v>
+        <v>0.2109722762833795</v>
       </c>
       <c r="I23" t="n">
-        <v>0.01886998468360548</v>
+        <v>7.077543849825483e-06</v>
       </c>
       <c r="J23" t="n">
-        <v>0.369235385145369</v>
+        <v>1.308242164555326e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1940526358799872</v>
+        <v>1.007998274768937e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2233463022837497</v>
+        <v>0.001026669339398064</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2520628027122147</v>
+        <v>0.001962499837835026</v>
       </c>
       <c r="N23" t="n">
-        <v>1.001982893097279</v>
+        <v>1.000002731682052</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2627936380656074</v>
+        <v>0.002046047518866374</v>
       </c>
       <c r="P23" t="n">
-        <v>283.5123080216327</v>
+        <v>186.9341447637582</v>
       </c>
       <c r="Q23" t="n">
-        <v>452.9360476783125</v>
+        <v>285.6630865780824</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9904059114882749</v>
+        <v>0.9999933731980798</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8245952054028094</v>
+        <v>0.6445570754954921</v>
       </c>
       <c r="D24" t="n">
-        <v>0.7655185029017285</v>
+        <v>0.9999500114594072</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9497379874474685</v>
+        <v>0.999983172800938</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9651550537234787</v>
+        <v>0.9999835170180081</v>
       </c>
       <c r="G24" t="n">
-        <v>0.06415571405462062</v>
+        <v>3.933955882773146e-06</v>
       </c>
       <c r="H24" t="n">
-        <v>1.172932669136228</v>
+        <v>0.2110062743207269</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0192257978748961</v>
+        <v>8.155126890726048e-06</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3744631812764979</v>
+        <v>1.326119291466201e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1968444982873805</v>
+        <v>1.070815990269403e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2210727759300165</v>
+        <v>0.001014710500856959</v>
       </c>
       <c r="M24" t="n">
-        <v>0.253289782767921</v>
+        <v>0.001983420248654618</v>
       </c>
       <c r="N24" t="n">
-        <v>1.002002244558969</v>
+        <v>1.000002790232387</v>
       </c>
       <c r="O24" t="n">
-        <v>0.264072853202484</v>
+        <v>0.002067858554885776</v>
       </c>
       <c r="P24" t="n">
-        <v>283.492884237099</v>
+        <v>186.8917301048073</v>
       </c>
       <c r="Q24" t="n">
-        <v>452.9166238937788</v>
+        <v>285.6206719191316</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9903139041382077</v>
+        <v>0.9999932075540207</v>
       </c>
       <c r="C25" t="n">
-        <v>0.824120739635523</v>
+        <v>0.6445055100985038</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7615702458113598</v>
+        <v>0.9999435715010966</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9490795585226908</v>
+        <v>0.9999829639763748</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9646922328429968</v>
+        <v>0.9999825817559231</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06477096762817497</v>
+        <v>4.032289351751315e-06</v>
       </c>
       <c r="H25" t="n">
-        <v>1.176105423906785</v>
+        <v>0.2110368857678884</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0195495265857621</v>
+        <v>9.205741222951558e-06</v>
       </c>
       <c r="J25" t="n">
-        <v>0.3793686233249843</v>
+        <v>1.342576354860983e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.199459045122735</v>
+        <v>1.131575238578069e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2190277252533153</v>
+        <v>0.0010039971219013</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2545014098746311</v>
+        <v>0.002008056112699871</v>
       </c>
       <c r="N25" t="n">
-        <v>1.002021446092896</v>
+        <v>1.000002859977254</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2653360617835406</v>
+        <v>0.002093543218666704</v>
       </c>
       <c r="P25" t="n">
-        <v>283.4737956128978</v>
+        <v>186.8423525318858</v>
       </c>
       <c r="Q25" t="n">
-        <v>452.8975352695777</v>
+        <v>285.57129434621</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9902242686999378</v>
+        <v>0.999993025591422</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8236864650483653</v>
+        <v>0.6444587743860808</v>
       </c>
       <c r="D26" t="n">
-        <v>0.757984853789767</v>
+        <v>0.9999373751392854</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9484657258362903</v>
+        <v>0.9999827722877292</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9642614413340815</v>
+        <v>0.9999816874734809</v>
       </c>
       <c r="G26" t="n">
-        <v>0.06537036021661921</v>
+        <v>4.140310210634636e-06</v>
       </c>
       <c r="H26" t="n">
-        <v>1.17900942007076</v>
+        <v>0.2110646301056604</v>
       </c>
       <c r="I26" t="n">
-        <v>0.01984350296838696</v>
+        <v>1.021661523991817e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.3839418134709376</v>
+        <v>1.357682969450978e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2018926530774132</v>
+        <v>1.189672246721398e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2171816987575496</v>
+        <v>0.0009943325162948839</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2556762801212095</v>
+        <v>0.002034775223614303</v>
       </c>
       <c r="N26" t="n">
-        <v>1.002040152619143</v>
+        <v>1.000002936593085</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2665609486888326</v>
+        <v>0.002121399817448948</v>
       </c>
       <c r="P26" t="n">
-        <v>283.4553726618911</v>
+        <v>186.7894796856584</v>
       </c>
       <c r="Q26" t="n">
-        <v>452.879112318571</v>
+        <v>285.5184214999826</v>
       </c>
     </row>
   </sheetData>
